--- a/data/confidence.xlsx
+++ b/data/confidence.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12.578125" customWidth="1" min="1" max="1"/>
@@ -456,11 +456,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1801904</v>
+        <v>1818456</v>
       </c>
       <c r="C2">
         <f>(B2/B6-1)*100</f>
@@ -470,11 +470,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1773656</v>
+        <v>1801904</v>
       </c>
       <c r="C3">
         <f>(B3/B7-1)*100</f>
@@ -484,11 +484,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1766328</v>
+        <v>1773656</v>
       </c>
       <c r="C4">
         <f>(B4/B8-1)*100</f>
@@ -498,11 +498,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1756560</v>
+        <v>1766328</v>
       </c>
       <c r="C5">
         <f>(B5/B9-1)*100</f>
@@ -512,35 +512,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1756560</v>
+      </c>
+      <c r="C6">
+        <f>(B6/B10-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>2024-09-01</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B7" t="n">
         <v>1729048</v>
       </c>
-      <c r="C6">
-        <f>(B6/B10-1)*100</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="C7">
+        <f>(B7/B11-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
         <v>45627</v>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B8" s="3" t="n">
         <v>47.9</v>
-      </c>
-      <c r="C7" s="1">
-        <f>(B7/B11-1)*100</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="n">
-        <v>45597</v>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>48.6</v>
       </c>
       <c r="C8" s="1">
         <f>(B8/B12-1)*100</f>
@@ -548,11 +550,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>45566</v>
+      <c r="A9" s="4" t="n">
+        <v>45597</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>49.1</v>
+        <v>48.6</v>
       </c>
       <c r="C9" s="1">
         <f>(B9/B13-1)*100</f>
@@ -560,11 +562,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n">
-        <v>45536</v>
+      <c r="A10" s="2" t="n">
+        <v>45566</v>
       </c>
       <c r="B10" s="3" t="n">
-        <v>49.5</v>
+        <v>49.1</v>
       </c>
       <c r="C10" s="1">
         <f>(B10/B14-1)*100</f>
@@ -572,11 +574,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>45505</v>
+      <c r="A11" s="4" t="n">
+        <v>45536</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>50.1</v>
+        <v>49.5</v>
       </c>
       <c r="C11" s="1">
         <f>(B11/B15-1)*100</f>
@@ -584,11 +586,11 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n">
-        <v>45474</v>
+      <c r="A12" s="2" t="n">
+        <v>45505</v>
       </c>
       <c r="B12" s="3" t="n">
-        <v>47</v>
+        <v>50.1</v>
       </c>
       <c r="C12" s="1">
         <f>(B12/B16-1)*100</f>
@@ -596,11 +598,11 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>45444</v>
+      <c r="A13" s="4" t="n">
+        <v>45474</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>47.1</v>
+        <v>47</v>
       </c>
       <c r="C13" s="1">
         <f>(B13/B17-1)*100</f>
@@ -608,11 +610,11 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n">
-        <v>45413</v>
+      <c r="A14" s="2" t="n">
+        <v>45444</v>
       </c>
       <c r="B14" s="3" t="n">
-        <v>47.2</v>
+        <v>47.1</v>
       </c>
       <c r="C14" s="1">
         <f>(B14/B18-1)*100</f>
@@ -620,11 +622,11 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>45383</v>
+      <c r="A15" s="4" t="n">
+        <v>45413</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>48</v>
+        <v>47.2</v>
       </c>
       <c r="C15" s="1">
         <f>(B15/B19-1)*100</f>
@@ -632,11 +634,11 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n">
-        <v>45352</v>
+      <c r="A16" s="2" t="n">
+        <v>45383</v>
       </c>
       <c r="B16" s="3" t="n">
-        <v>47.89</v>
+        <v>48</v>
       </c>
       <c r="C16" s="1">
         <f>(B16/B20-1)*100</f>
@@ -644,11 +646,11 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>45323</v>
+      <c r="A17" s="4" t="n">
+        <v>45352</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>47.38</v>
+        <v>47.89</v>
       </c>
       <c r="C17" s="1">
         <f>(B17/B21-1)*100</f>
@@ -656,11 +658,11 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n">
-        <v>45292</v>
+      <c r="A18" s="2" t="n">
+        <v>45323</v>
       </c>
       <c r="B18" s="3" t="n">
-        <v>49.46</v>
+        <v>47.38</v>
       </c>
       <c r="C18" s="1">
         <f>(B18/B22-1)*100</f>
@@ -668,11 +670,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>45261</v>
+      <c r="A19" s="4" t="n">
+        <v>45292</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>46.57</v>
+        <v>49.46</v>
       </c>
       <c r="C19" s="1">
         <f>(B19/B23-1)*100</f>
@@ -680,11 +682,11 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="n">
-        <v>45231</v>
+      <c r="A20" s="2" t="n">
+        <v>45261</v>
       </c>
       <c r="B20" s="3" t="n">
-        <v>47.26</v>
+        <v>46.57</v>
       </c>
       <c r="C20" s="1">
         <f>(B20/B24-1)*100</f>
@@ -692,11 +694,11 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>45200</v>
+      <c r="A21" s="4" t="n">
+        <v>45231</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>45.56</v>
+        <v>47.26</v>
       </c>
       <c r="C21" s="1">
         <f>(B21/B25-1)*100</f>
@@ -704,11 +706,11 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="n">
-        <v>45170</v>
+      <c r="A22" s="2" t="n">
+        <v>45200</v>
       </c>
       <c r="B22" s="3" t="n">
-        <v>47.66</v>
+        <v>45.56</v>
       </c>
       <c r="C22" s="1">
         <f>(B22/B26-1)*100</f>
@@ -716,11 +718,11 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>45139</v>
+      <c r="A23" s="4" t="n">
+        <v>45170</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>46.9</v>
+        <v>47.66</v>
       </c>
       <c r="C23" s="1">
         <f>(B23/B27-1)*100</f>
@@ -728,11 +730,11 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="n">
-        <v>45108</v>
+      <c r="A24" s="2" t="n">
+        <v>45139</v>
       </c>
       <c r="B24" s="3" t="n">
-        <v>49.55</v>
+        <v>46.9</v>
       </c>
       <c r="C24" s="1">
         <f>(B24/B28-1)*100</f>
@@ -740,11 +742,11 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>45078</v>
+      <c r="A25" s="4" t="n">
+        <v>45108</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>51.43</v>
+        <v>49.55</v>
       </c>
       <c r="C25" s="1">
         <f>(B25/B29-1)*100</f>
@@ -752,11 +754,11 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="n">
-        <v>45047</v>
+      <c r="A26" s="2" t="n">
+        <v>45078</v>
       </c>
       <c r="B26" s="3" t="n">
-        <v>49.54</v>
+        <v>51.43</v>
       </c>
       <c r="C26" s="1">
         <f>(B26/B30-1)*100</f>
@@ -764,11 +766,11 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>45017</v>
+      <c r="A27" s="4" t="n">
+        <v>45047</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>49.24</v>
+        <v>49.54</v>
       </c>
       <c r="C27" s="1">
         <f>(B27/B31-1)*100</f>
@@ -776,11 +778,11 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="n">
-        <v>44986</v>
+      <c r="A28" s="2" t="n">
+        <v>45017</v>
       </c>
       <c r="B28" s="3" t="n">
-        <v>47.28</v>
+        <v>49.24</v>
       </c>
       <c r="C28" s="1">
         <f>(B28/B32-1)*100</f>
@@ -788,11 +790,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>44958</v>
+      <c r="A29" s="4" t="n">
+        <v>44986</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>47.49</v>
+        <v>47.28</v>
       </c>
       <c r="C29" s="1">
         <f>(B29/B33-1)*100</f>
@@ -800,11 +802,11 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="n">
-        <v>44927</v>
+      <c r="A30" s="2" t="n">
+        <v>44958</v>
       </c>
       <c r="B30" s="3" t="n">
-        <v>48.81</v>
+        <v>47.49</v>
       </c>
       <c r="C30" s="1">
         <f>(B30/B34-1)*100</f>
@@ -812,11 +814,11 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
-        <v>44896</v>
+      <c r="A31" s="4" t="n">
+        <v>44927</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>49.34</v>
+        <v>48.81</v>
       </c>
       <c r="C31" s="1">
         <f>(B31/B35-1)*100</f>
@@ -824,23 +826,23 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="n">
+      <c r="A32" s="2" t="n">
+        <v>44896</v>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="C32" s="1">
+        <f>(B32/B36-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
         <v>44866</v>
       </c>
-      <c r="B32" s="3" t="n">
+      <c r="B33" s="3" t="n">
         <v>46.62</v>
-      </c>
-      <c r="C32">
-        <f>(B32/B36-1)*100</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
-        <v>44835</v>
-      </c>
-      <c r="B33" s="3" t="n">
-        <v>48.51</v>
       </c>
       <c r="C33">
         <f>(B33/B37-1)*100</f>
@@ -848,11 +850,11 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="n">
-        <v>44805</v>
+      <c r="A34" s="2" t="n">
+        <v>44835</v>
       </c>
       <c r="B34" s="3" t="n">
-        <v>50.14</v>
+        <v>48.51</v>
       </c>
       <c r="C34">
         <f>(B34/B38-1)*100</f>
@@ -860,11 +862,11 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
-        <v>44774</v>
+      <c r="A35" s="4" t="n">
+        <v>44805</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>50.32</v>
+        <v>50.14</v>
       </c>
       <c r="C35">
         <f>(B35/B39-1)*100</f>
@@ -872,11 +874,11 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="n">
-        <v>44743</v>
+      <c r="A36" s="2" t="n">
+        <v>44774</v>
       </c>
       <c r="B36" s="3" t="n">
-        <v>50.35</v>
+        <v>50.32</v>
       </c>
       <c r="C36">
         <f>(B36/B40-1)*100</f>
@@ -884,11 +886,11 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
-        <v>44713</v>
+      <c r="A37" s="4" t="n">
+        <v>44743</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>50.42</v>
+        <v>50.35</v>
       </c>
       <c r="C37">
         <f>(B37/B41-1)*100</f>
@@ -896,11 +898,11 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="n">
-        <v>44682</v>
+      <c r="A38" s="2" t="n">
+        <v>44713</v>
       </c>
       <c r="B38" s="3" t="n">
-        <v>52.23</v>
+        <v>50.42</v>
       </c>
       <c r="C38">
         <f>(B38/B42-1)*100</f>
@@ -908,11 +910,11 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
-        <v>44652</v>
+      <c r="A39" s="4" t="n">
+        <v>44682</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v>49.98</v>
+        <v>52.23</v>
       </c>
       <c r="C39">
         <f>(B39/B43-1)*100</f>
@@ -920,11 +922,11 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="n">
-        <v>44621</v>
+      <c r="A40" s="2" t="n">
+        <v>44652</v>
       </c>
       <c r="B40" s="3" t="n">
-        <v>49.09</v>
+        <v>49.98</v>
       </c>
       <c r="C40">
         <f>(B40/B44-1)*100</f>
@@ -932,11 +934,11 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
-        <v>44593</v>
+      <c r="A41" s="4" t="n">
+        <v>44621</v>
       </c>
       <c r="B41" s="3" t="n">
-        <v>51.41</v>
+        <v>49.09</v>
       </c>
       <c r="C41">
         <f>(B41/B45-1)*100</f>
@@ -944,11 +946,11 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="n">
-        <v>44562</v>
+      <c r="A42" s="2" t="n">
+        <v>44593</v>
       </c>
       <c r="B42" s="3" t="n">
-        <v>51.51</v>
+        <v>51.41</v>
       </c>
       <c r="C42">
         <f>(B42/B46-1)*100</f>
@@ -956,10 +958,22 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="4" t="n">
+        <v>44562</v>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>51.51</v>
+      </c>
+      <c r="C43">
+        <f>(B43/B47-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
         <v>44531</v>
       </c>
-      <c r="B43" s="3" t="n">
+      <c r="B44" s="3" t="n">
         <v>52.28</v>
       </c>
     </row>

--- a/data/confidence.xlsx
+++ b/data/confidence.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12.578125" customWidth="1" min="1" max="1"/>
@@ -456,11 +456,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1818456</v>
+        <v>1811968</v>
       </c>
       <c r="C2">
         <f>(B2/B6-1)*100</f>
@@ -470,11 +470,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1801904</v>
+        <v>1818456</v>
       </c>
       <c r="C3">
         <f>(B3/B7-1)*100</f>
@@ -484,11 +484,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1773656</v>
+        <v>1801904</v>
       </c>
       <c r="C4">
         <f>(B4/B8-1)*100</f>
@@ -498,11 +498,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1766328</v>
+        <v>1773656</v>
       </c>
       <c r="C5">
         <f>(B5/B9-1)*100</f>
@@ -512,11 +512,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1756560</v>
+        <v>1766328</v>
       </c>
       <c r="C6">
         <f>(B6/B10-1)*100</f>
@@ -526,35 +526,37 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1756560</v>
+      </c>
+      <c r="C7">
+        <f>(B7/B11-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>2024-09-01</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B8" t="n">
         <v>1729048</v>
       </c>
-      <c r="C7">
-        <f>(B7/B11-1)*100</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="C8">
+        <f>(B8/B12-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
         <v>45627</v>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B9" s="3" t="n">
         <v>47.9</v>
-      </c>
-      <c r="C8" s="1">
-        <f>(B8/B12-1)*100</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="n">
-        <v>45597</v>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>48.6</v>
       </c>
       <c r="C9" s="1">
         <f>(B9/B13-1)*100</f>
@@ -562,11 +564,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>45566</v>
+      <c r="A10" s="4" t="n">
+        <v>45597</v>
       </c>
       <c r="B10" s="3" t="n">
-        <v>49.1</v>
+        <v>48.6</v>
       </c>
       <c r="C10" s="1">
         <f>(B10/B14-1)*100</f>
@@ -574,11 +576,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
-        <v>45536</v>
+      <c r="A11" s="2" t="n">
+        <v>45566</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>49.5</v>
+        <v>49.1</v>
       </c>
       <c r="C11" s="1">
         <f>(B11/B15-1)*100</f>
@@ -586,11 +588,11 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>45505</v>
+      <c r="A12" s="4" t="n">
+        <v>45536</v>
       </c>
       <c r="B12" s="3" t="n">
-        <v>50.1</v>
+        <v>49.5</v>
       </c>
       <c r="C12" s="1">
         <f>(B12/B16-1)*100</f>
@@ -598,11 +600,11 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
-        <v>45474</v>
+      <c r="A13" s="2" t="n">
+        <v>45505</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>47</v>
+        <v>50.1</v>
       </c>
       <c r="C13" s="1">
         <f>(B13/B17-1)*100</f>
@@ -610,11 +612,11 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>45444</v>
+      <c r="A14" s="4" t="n">
+        <v>45474</v>
       </c>
       <c r="B14" s="3" t="n">
-        <v>47.1</v>
+        <v>47</v>
       </c>
       <c r="C14" s="1">
         <f>(B14/B18-1)*100</f>
@@ -622,11 +624,11 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n">
-        <v>45413</v>
+      <c r="A15" s="2" t="n">
+        <v>45444</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>47.2</v>
+        <v>47.1</v>
       </c>
       <c r="C15" s="1">
         <f>(B15/B19-1)*100</f>
@@ -634,11 +636,11 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>45383</v>
+      <c r="A16" s="4" t="n">
+        <v>45413</v>
       </c>
       <c r="B16" s="3" t="n">
-        <v>48</v>
+        <v>47.2</v>
       </c>
       <c r="C16" s="1">
         <f>(B16/B20-1)*100</f>
@@ -646,11 +648,11 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
-        <v>45352</v>
+      <c r="A17" s="2" t="n">
+        <v>45383</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>47.89</v>
+        <v>48</v>
       </c>
       <c r="C17" s="1">
         <f>(B17/B21-1)*100</f>
@@ -658,11 +660,11 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>45323</v>
+      <c r="A18" s="4" t="n">
+        <v>45352</v>
       </c>
       <c r="B18" s="3" t="n">
-        <v>47.38</v>
+        <v>47.89</v>
       </c>
       <c r="C18" s="1">
         <f>(B18/B22-1)*100</f>
@@ -670,11 +672,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n">
-        <v>45292</v>
+      <c r="A19" s="2" t="n">
+        <v>45323</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>49.46</v>
+        <v>47.38</v>
       </c>
       <c r="C19" s="1">
         <f>(B19/B23-1)*100</f>
@@ -682,11 +684,11 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>45261</v>
+      <c r="A20" s="4" t="n">
+        <v>45292</v>
       </c>
       <c r="B20" s="3" t="n">
-        <v>46.57</v>
+        <v>49.46</v>
       </c>
       <c r="C20" s="1">
         <f>(B20/B24-1)*100</f>
@@ -694,11 +696,11 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n">
-        <v>45231</v>
+      <c r="A21" s="2" t="n">
+        <v>45261</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>47.26</v>
+        <v>46.57</v>
       </c>
       <c r="C21" s="1">
         <f>(B21/B25-1)*100</f>
@@ -706,11 +708,11 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>45200</v>
+      <c r="A22" s="4" t="n">
+        <v>45231</v>
       </c>
       <c r="B22" s="3" t="n">
-        <v>45.56</v>
+        <v>47.26</v>
       </c>
       <c r="C22" s="1">
         <f>(B22/B26-1)*100</f>
@@ -718,11 +720,11 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="n">
-        <v>45170</v>
+      <c r="A23" s="2" t="n">
+        <v>45200</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>47.66</v>
+        <v>45.56</v>
       </c>
       <c r="C23" s="1">
         <f>(B23/B27-1)*100</f>
@@ -730,11 +732,11 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>45139</v>
+      <c r="A24" s="4" t="n">
+        <v>45170</v>
       </c>
       <c r="B24" s="3" t="n">
-        <v>46.9</v>
+        <v>47.66</v>
       </c>
       <c r="C24" s="1">
         <f>(B24/B28-1)*100</f>
@@ -742,11 +744,11 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="n">
-        <v>45108</v>
+      <c r="A25" s="2" t="n">
+        <v>45139</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>49.55</v>
+        <v>46.9</v>
       </c>
       <c r="C25" s="1">
         <f>(B25/B29-1)*100</f>
@@ -754,11 +756,11 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>45078</v>
+      <c r="A26" s="4" t="n">
+        <v>45108</v>
       </c>
       <c r="B26" s="3" t="n">
-        <v>51.43</v>
+        <v>49.55</v>
       </c>
       <c r="C26" s="1">
         <f>(B26/B30-1)*100</f>
@@ -766,11 +768,11 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="n">
-        <v>45047</v>
+      <c r="A27" s="2" t="n">
+        <v>45078</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>49.54</v>
+        <v>51.43</v>
       </c>
       <c r="C27" s="1">
         <f>(B27/B31-1)*100</f>
@@ -778,11 +780,11 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>45017</v>
+      <c r="A28" s="4" t="n">
+        <v>45047</v>
       </c>
       <c r="B28" s="3" t="n">
-        <v>49.24</v>
+        <v>49.54</v>
       </c>
       <c r="C28" s="1">
         <f>(B28/B32-1)*100</f>
@@ -790,11 +792,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="n">
-        <v>44986</v>
+      <c r="A29" s="2" t="n">
+        <v>45017</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>47.28</v>
+        <v>49.24</v>
       </c>
       <c r="C29" s="1">
         <f>(B29/B33-1)*100</f>
@@ -802,11 +804,11 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>44958</v>
+      <c r="A30" s="4" t="n">
+        <v>44986</v>
       </c>
       <c r="B30" s="3" t="n">
-        <v>47.49</v>
+        <v>47.28</v>
       </c>
       <c r="C30" s="1">
         <f>(B30/B34-1)*100</f>
@@ -814,11 +816,11 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="n">
-        <v>44927</v>
+      <c r="A31" s="2" t="n">
+        <v>44958</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>48.81</v>
+        <v>47.49</v>
       </c>
       <c r="C31" s="1">
         <f>(B31/B35-1)*100</f>
@@ -826,11 +828,11 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
-        <v>44896</v>
+      <c r="A32" s="4" t="n">
+        <v>44927</v>
       </c>
       <c r="B32" s="3" t="n">
-        <v>49.34</v>
+        <v>48.81</v>
       </c>
       <c r="C32" s="1">
         <f>(B32/B36-1)*100</f>
@@ -838,23 +840,23 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="n">
+      <c r="A33" s="2" t="n">
+        <v>44896</v>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="C33" s="1">
+        <f>(B33/B37-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
         <v>44866</v>
       </c>
-      <c r="B33" s="3" t="n">
+      <c r="B34" s="3" t="n">
         <v>46.62</v>
-      </c>
-      <c r="C33">
-        <f>(B33/B37-1)*100</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="n">
-        <v>44835</v>
-      </c>
-      <c r="B34" s="3" t="n">
-        <v>48.51</v>
       </c>
       <c r="C34">
         <f>(B34/B38-1)*100</f>
@@ -862,11 +864,11 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="n">
-        <v>44805</v>
+      <c r="A35" s="2" t="n">
+        <v>44835</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>50.14</v>
+        <v>48.51</v>
       </c>
       <c r="C35">
         <f>(B35/B39-1)*100</f>
@@ -874,11 +876,11 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
-        <v>44774</v>
+      <c r="A36" s="4" t="n">
+        <v>44805</v>
       </c>
       <c r="B36" s="3" t="n">
-        <v>50.32</v>
+        <v>50.14</v>
       </c>
       <c r="C36">
         <f>(B36/B40-1)*100</f>
@@ -886,11 +888,11 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="n">
-        <v>44743</v>
+      <c r="A37" s="2" t="n">
+        <v>44774</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>50.35</v>
+        <v>50.32</v>
       </c>
       <c r="C37">
         <f>(B37/B41-1)*100</f>
@@ -898,11 +900,11 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
-        <v>44713</v>
+      <c r="A38" s="4" t="n">
+        <v>44743</v>
       </c>
       <c r="B38" s="3" t="n">
-        <v>50.42</v>
+        <v>50.35</v>
       </c>
       <c r="C38">
         <f>(B38/B42-1)*100</f>
@@ -910,11 +912,11 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="n">
-        <v>44682</v>
+      <c r="A39" s="2" t="n">
+        <v>44713</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v>52.23</v>
+        <v>50.42</v>
       </c>
       <c r="C39">
         <f>(B39/B43-1)*100</f>
@@ -922,11 +924,11 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
-        <v>44652</v>
+      <c r="A40" s="4" t="n">
+        <v>44682</v>
       </c>
       <c r="B40" s="3" t="n">
-        <v>49.98</v>
+        <v>52.23</v>
       </c>
       <c r="C40">
         <f>(B40/B44-1)*100</f>
@@ -934,11 +936,11 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="n">
-        <v>44621</v>
+      <c r="A41" s="2" t="n">
+        <v>44652</v>
       </c>
       <c r="B41" s="3" t="n">
-        <v>49.09</v>
+        <v>49.98</v>
       </c>
       <c r="C41">
         <f>(B41/B45-1)*100</f>
@@ -946,11 +948,11 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
-        <v>44593</v>
+      <c r="A42" s="4" t="n">
+        <v>44621</v>
       </c>
       <c r="B42" s="3" t="n">
-        <v>51.41</v>
+        <v>49.09</v>
       </c>
       <c r="C42">
         <f>(B42/B46-1)*100</f>
@@ -958,11 +960,11 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="n">
-        <v>44562</v>
+      <c r="A43" s="2" t="n">
+        <v>44593</v>
       </c>
       <c r="B43" s="3" t="n">
-        <v>51.51</v>
+        <v>51.41</v>
       </c>
       <c r="C43">
         <f>(B43/B47-1)*100</f>
@@ -970,10 +972,22 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="4" t="n">
+        <v>44562</v>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>51.51</v>
+      </c>
+      <c r="C44">
+        <f>(B44/B48-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
         <v>44531</v>
       </c>
-      <c r="B44" s="3" t="n">
+      <c r="B45" s="3" t="n">
         <v>52.28</v>
       </c>
     </row>

--- a/data/confidence.xlsx
+++ b/data/confidence.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12.578125" customWidth="1" min="1" max="1"/>
@@ -456,11 +456,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1811968</v>
+        <v>1860216</v>
       </c>
       <c r="C2">
         <f>(B2/B6-1)*100</f>
@@ -470,11 +470,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1818456</v>
+        <v>1811968</v>
       </c>
       <c r="C3">
         <f>(B3/B7-1)*100</f>
@@ -484,11 +484,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1801904</v>
+        <v>1818456</v>
       </c>
       <c r="C4">
         <f>(B4/B8-1)*100</f>
@@ -498,11 +498,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1773656</v>
+        <v>1801904</v>
       </c>
       <c r="C5">
         <f>(B5/B9-1)*100</f>
@@ -512,11 +512,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1766328</v>
+        <v>1773656</v>
       </c>
       <c r="C6">
         <f>(B6/B10-1)*100</f>
@@ -526,11 +526,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1756560</v>
+        <v>1766328</v>
       </c>
       <c r="C7">
         <f>(B7/B11-1)*100</f>
@@ -540,35 +540,37 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1756560</v>
+      </c>
+      <c r="C8">
+        <f>(B8/B12-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>2024-09-01</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B9" t="n">
         <v>1729048</v>
       </c>
-      <c r="C8">
-        <f>(B8/B12-1)*100</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="C9">
+        <f>(B9/B13-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
         <v>45627</v>
       </c>
-      <c r="B9" s="3" t="n">
+      <c r="B10" s="3" t="n">
         <v>47.9</v>
-      </c>
-      <c r="C9" s="1">
-        <f>(B9/B13-1)*100</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="n">
-        <v>45597</v>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>48.6</v>
       </c>
       <c r="C10" s="1">
         <f>(B10/B14-1)*100</f>
@@ -576,11 +578,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>45566</v>
+      <c r="A11" s="4" t="n">
+        <v>45597</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>49.1</v>
+        <v>48.6</v>
       </c>
       <c r="C11" s="1">
         <f>(B11/B15-1)*100</f>
@@ -588,11 +590,11 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n">
-        <v>45536</v>
+      <c r="A12" s="2" t="n">
+        <v>45566</v>
       </c>
       <c r="B12" s="3" t="n">
-        <v>49.5</v>
+        <v>49.1</v>
       </c>
       <c r="C12" s="1">
         <f>(B12/B16-1)*100</f>
@@ -600,11 +602,11 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>45505</v>
+      <c r="A13" s="4" t="n">
+        <v>45536</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>50.1</v>
+        <v>49.5</v>
       </c>
       <c r="C13" s="1">
         <f>(B13/B17-1)*100</f>
@@ -612,11 +614,11 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n">
-        <v>45474</v>
+      <c r="A14" s="2" t="n">
+        <v>45505</v>
       </c>
       <c r="B14" s="3" t="n">
-        <v>47</v>
+        <v>50.1</v>
       </c>
       <c r="C14" s="1">
         <f>(B14/B18-1)*100</f>
@@ -624,11 +626,11 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>45444</v>
+      <c r="A15" s="4" t="n">
+        <v>45474</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>47.1</v>
+        <v>47</v>
       </c>
       <c r="C15" s="1">
         <f>(B15/B19-1)*100</f>
@@ -636,11 +638,11 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n">
-        <v>45413</v>
+      <c r="A16" s="2" t="n">
+        <v>45444</v>
       </c>
       <c r="B16" s="3" t="n">
-        <v>47.2</v>
+        <v>47.1</v>
       </c>
       <c r="C16" s="1">
         <f>(B16/B20-1)*100</f>
@@ -648,11 +650,11 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>45383</v>
+      <c r="A17" s="4" t="n">
+        <v>45413</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>48</v>
+        <v>47.2</v>
       </c>
       <c r="C17" s="1">
         <f>(B17/B21-1)*100</f>
@@ -660,11 +662,11 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n">
-        <v>45352</v>
+      <c r="A18" s="2" t="n">
+        <v>45383</v>
       </c>
       <c r="B18" s="3" t="n">
-        <v>47.89</v>
+        <v>48</v>
       </c>
       <c r="C18" s="1">
         <f>(B18/B22-1)*100</f>
@@ -672,11 +674,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>45323</v>
+      <c r="A19" s="4" t="n">
+        <v>45352</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>47.38</v>
+        <v>47.89</v>
       </c>
       <c r="C19" s="1">
         <f>(B19/B23-1)*100</f>
@@ -684,11 +686,11 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="n">
-        <v>45292</v>
+      <c r="A20" s="2" t="n">
+        <v>45323</v>
       </c>
       <c r="B20" s="3" t="n">
-        <v>49.46</v>
+        <v>47.38</v>
       </c>
       <c r="C20" s="1">
         <f>(B20/B24-1)*100</f>
@@ -696,11 +698,11 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>45261</v>
+      <c r="A21" s="4" t="n">
+        <v>45292</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>46.57</v>
+        <v>49.46</v>
       </c>
       <c r="C21" s="1">
         <f>(B21/B25-1)*100</f>
@@ -708,11 +710,11 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="n">
-        <v>45231</v>
+      <c r="A22" s="2" t="n">
+        <v>45261</v>
       </c>
       <c r="B22" s="3" t="n">
-        <v>47.26</v>
+        <v>46.57</v>
       </c>
       <c r="C22" s="1">
         <f>(B22/B26-1)*100</f>
@@ -720,11 +722,11 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>45200</v>
+      <c r="A23" s="4" t="n">
+        <v>45231</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>45.56</v>
+        <v>47.26</v>
       </c>
       <c r="C23" s="1">
         <f>(B23/B27-1)*100</f>
@@ -732,11 +734,11 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="n">
-        <v>45170</v>
+      <c r="A24" s="2" t="n">
+        <v>45200</v>
       </c>
       <c r="B24" s="3" t="n">
-        <v>47.66</v>
+        <v>45.56</v>
       </c>
       <c r="C24" s="1">
         <f>(B24/B28-1)*100</f>
@@ -744,11 +746,11 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>45139</v>
+      <c r="A25" s="4" t="n">
+        <v>45170</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>46.9</v>
+        <v>47.66</v>
       </c>
       <c r="C25" s="1">
         <f>(B25/B29-1)*100</f>
@@ -756,11 +758,11 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="n">
-        <v>45108</v>
+      <c r="A26" s="2" t="n">
+        <v>45139</v>
       </c>
       <c r="B26" s="3" t="n">
-        <v>49.55</v>
+        <v>46.9</v>
       </c>
       <c r="C26" s="1">
         <f>(B26/B30-1)*100</f>
@@ -768,11 +770,11 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>45078</v>
+      <c r="A27" s="4" t="n">
+        <v>45108</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>51.43</v>
+        <v>49.55</v>
       </c>
       <c r="C27" s="1">
         <f>(B27/B31-1)*100</f>
@@ -780,11 +782,11 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="n">
-        <v>45047</v>
+      <c r="A28" s="2" t="n">
+        <v>45078</v>
       </c>
       <c r="B28" s="3" t="n">
-        <v>49.54</v>
+        <v>51.43</v>
       </c>
       <c r="C28" s="1">
         <f>(B28/B32-1)*100</f>
@@ -792,11 +794,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>45017</v>
+      <c r="A29" s="4" t="n">
+        <v>45047</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>49.24</v>
+        <v>49.54</v>
       </c>
       <c r="C29" s="1">
         <f>(B29/B33-1)*100</f>
@@ -804,11 +806,11 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="n">
-        <v>44986</v>
+      <c r="A30" s="2" t="n">
+        <v>45017</v>
       </c>
       <c r="B30" s="3" t="n">
-        <v>47.28</v>
+        <v>49.24</v>
       </c>
       <c r="C30" s="1">
         <f>(B30/B34-1)*100</f>
@@ -816,11 +818,11 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
-        <v>44958</v>
+      <c r="A31" s="4" t="n">
+        <v>44986</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>47.49</v>
+        <v>47.28</v>
       </c>
       <c r="C31" s="1">
         <f>(B31/B35-1)*100</f>
@@ -828,11 +830,11 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="n">
-        <v>44927</v>
+      <c r="A32" s="2" t="n">
+        <v>44958</v>
       </c>
       <c r="B32" s="3" t="n">
-        <v>48.81</v>
+        <v>47.49</v>
       </c>
       <c r="C32" s="1">
         <f>(B32/B36-1)*100</f>
@@ -840,11 +842,11 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
-        <v>44896</v>
+      <c r="A33" s="4" t="n">
+        <v>44927</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>49.34</v>
+        <v>48.81</v>
       </c>
       <c r="C33" s="1">
         <f>(B33/B37-1)*100</f>
@@ -852,23 +854,23 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="n">
+      <c r="A34" s="2" t="n">
+        <v>44896</v>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="C34" s="1">
+        <f>(B34/B38-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
         <v>44866</v>
       </c>
-      <c r="B34" s="3" t="n">
+      <c r="B35" s="3" t="n">
         <v>46.62</v>
-      </c>
-      <c r="C34">
-        <f>(B34/B38-1)*100</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="n">
-        <v>44835</v>
-      </c>
-      <c r="B35" s="3" t="n">
-        <v>48.51</v>
       </c>
       <c r="C35">
         <f>(B35/B39-1)*100</f>
@@ -876,11 +878,11 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="n">
-        <v>44805</v>
+      <c r="A36" s="2" t="n">
+        <v>44835</v>
       </c>
       <c r="B36" s="3" t="n">
-        <v>50.14</v>
+        <v>48.51</v>
       </c>
       <c r="C36">
         <f>(B36/B40-1)*100</f>
@@ -888,11 +890,11 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
-        <v>44774</v>
+      <c r="A37" s="4" t="n">
+        <v>44805</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>50.32</v>
+        <v>50.14</v>
       </c>
       <c r="C37">
         <f>(B37/B41-1)*100</f>
@@ -900,11 +902,11 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="n">
-        <v>44743</v>
+      <c r="A38" s="2" t="n">
+        <v>44774</v>
       </c>
       <c r="B38" s="3" t="n">
-        <v>50.35</v>
+        <v>50.32</v>
       </c>
       <c r="C38">
         <f>(B38/B42-1)*100</f>
@@ -912,11 +914,11 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
-        <v>44713</v>
+      <c r="A39" s="4" t="n">
+        <v>44743</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v>50.42</v>
+        <v>50.35</v>
       </c>
       <c r="C39">
         <f>(B39/B43-1)*100</f>
@@ -924,11 +926,11 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="n">
-        <v>44682</v>
+      <c r="A40" s="2" t="n">
+        <v>44713</v>
       </c>
       <c r="B40" s="3" t="n">
-        <v>52.23</v>
+        <v>50.42</v>
       </c>
       <c r="C40">
         <f>(B40/B44-1)*100</f>
@@ -936,11 +938,11 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
-        <v>44652</v>
+      <c r="A41" s="4" t="n">
+        <v>44682</v>
       </c>
       <c r="B41" s="3" t="n">
-        <v>49.98</v>
+        <v>52.23</v>
       </c>
       <c r="C41">
         <f>(B41/B45-1)*100</f>
@@ -948,11 +950,11 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="n">
-        <v>44621</v>
+      <c r="A42" s="2" t="n">
+        <v>44652</v>
       </c>
       <c r="B42" s="3" t="n">
-        <v>49.09</v>
+        <v>49.98</v>
       </c>
       <c r="C42">
         <f>(B42/B46-1)*100</f>
@@ -960,11 +962,11 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
-        <v>44593</v>
+      <c r="A43" s="4" t="n">
+        <v>44621</v>
       </c>
       <c r="B43" s="3" t="n">
-        <v>51.41</v>
+        <v>49.09</v>
       </c>
       <c r="C43">
         <f>(B43/B47-1)*100</f>
@@ -972,11 +974,11 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="n">
-        <v>44562</v>
+      <c r="A44" s="2" t="n">
+        <v>44593</v>
       </c>
       <c r="B44" s="3" t="n">
-        <v>51.51</v>
+        <v>51.41</v>
       </c>
       <c r="C44">
         <f>(B44/B48-1)*100</f>
@@ -984,10 +986,22 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="4" t="n">
+        <v>44562</v>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>51.51</v>
+      </c>
+      <c r="C45">
+        <f>(B45/B49-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
         <v>44531</v>
       </c>
-      <c r="B45" s="3" t="n">
+      <c r="B46" s="3" t="n">
         <v>52.28</v>
       </c>
     </row>
